--- a/exports/xlsx/UWRDB_release.xlsx
+++ b/exports/xlsx/UWRDB_release.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="owner" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="distillery" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brand" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="region" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="owner" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="distillery" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="brand" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="evidence" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/xlsx/UWRDB_release.xlsx
+++ b/exports/xlsx/UWRDB_release.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="region" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="owner" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="distillery" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="brand" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="owner" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="distillery" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brand" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,28 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AVR-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Temporary value pending curation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -614,45 +636,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AVP-DIAGEO</t>
+          <t>AVP-UNKNOWN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diageo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.diageo.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Temporary value pending curation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVP-LVMH</t>
+          <t>AVP-DIAGEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LVMH</t>
+          <t>Diageo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.lvmh.com</t>
+          <t>https://www.diageo.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -660,22 +678,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVP-SUNTORY-GLOBAL-SPIRITS</t>
+          <t>AVP-LVMH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Suntory Global Spirits</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.suntoryglobalspirits.com</t>
+          <t>https://www.lvmh.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -729,45 +747,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AVO-DIAGEO</t>
+          <t>AVO-UNKNOWN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diageo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AVP-DIAGEO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://www.diageo.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Temporary value pending curation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVO-ARDBEG</t>
+          <t>AVO-DIAGEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Ardbeg Distillery Ltd.</t>
+          <t>Diageo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AVP-LVMH</t>
+          <t>AVP-DIAGEO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,7 +791,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.ardbeg.com</t>
+          <t>https://www.diageo.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -785,17 +799,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVO-BEAM-SUNTORY</t>
+          <t>AVO-ARDBEG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Beam Suntory</t>
+          <t>The Ardbeg Distillery Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AVP-SUNTORY-GLOBAL-SPIRITS</t>
+          <t>AVP-LVMH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,7 +819,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.suntoryglobalspirits.com</t>
+          <t>https://www.ardbeg.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -821,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,7 +910,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Canonical baseline</t>
+          <t>Canonical operating baseline</t>
         </is>
       </c>
     </row>
@@ -929,36 +943,6 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AVS-OWNER-WEBSITE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Official</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Owner corporate website</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -971,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,33 +1066,25 @@
           <t>Operating</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AVO-ARDBEG</t>
+          <t>AVO-UNKNOWN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AVP-LVMH</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://www.ardbeg.com</t>
-        </is>
-      </c>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Seed record; verify before Gold</t>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1119,78 @@
           <t>Operating</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AVO-DIAGEO</t>
+          <t>AVO-UNKNOWN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AVP-DIAGEO</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://www.malts.com</t>
-        </is>
-      </c>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Seed record; verify before Gold</t>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AVD-CAMERONBRIDGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cameronbridge</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cameronbridge</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AVR-LOWLANDS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AVO-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
         </is>
       </c>
     </row>
@@ -1184,113 +1205,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>brand_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>distillery_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>brand_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>brand_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AVB-ARDBEG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AVD-ARDBEG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ardbeg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.ardbeg.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AVB-CAOL-ILA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AVD-CAOL-ILA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Caol Ila</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.malts.com</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1301,151 +1218,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>evidence_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>entity_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>field_name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>field_value</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verified_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AVE-000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>distillery</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AVD-ARDBEG</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>official_name</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ardbeg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AVS-OFFICIAL-DISTILLERY-WEBSITE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Seed example</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AVE-000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>distillery</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AVD-CAOL-ILA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>owner_id</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AVO-DIAGEO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AVS-OWNER-WEBSITE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Seed example</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/xlsx/UWRDB_release.xlsx
+++ b/exports/xlsx/UWRDB_release.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="owner" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="distillery" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brand" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="distillery" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brand" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,46 +836,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>source_id</t>
+          <t>field_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>entity_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>authority</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>gold_required</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>reliability</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>last_checked</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -883,66 +869,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AVS-SWA-OPERATING-LIST</t>
+          <t>official_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>distillery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scotch Whisky Association</t>
+          <t>Official or preferred current distillery name</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Current operating Scotch whisky distillery list</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Canonical operating baseline</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Core identity</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVS-OFFICIAL-DISTILLERY-WEBSITE</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>distillery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Distillery</t>
+          <t>Controlled region classification</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Official distillery website</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Core identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Production type: Malt, Grain, Malt &amp; Grain, Unknown</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Core identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Operating status</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Core identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>founded_year</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Year the distillery was founded</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Requires evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>owner_id</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Current operating owner</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gold requires curated owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>parent_company_id</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ultimate controlling parent company</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Gold requires curated parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Official website</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prefer HTTPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WGS84 latitude</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gold geography target</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WGS84 longitude</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gold geography target</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -955,81 +1147,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>distillery_id</t>
+          <t>source_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>official_name</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>preferred_name</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>region_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>url</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>reliability</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>founded_year</t>
+          <t>last_checked</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>owner_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>parent_company_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1038,161 +1195,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AVD-ARDBEG</t>
+          <t>AVS-SWA-OPERATING-LIST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ardbeg</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ardbeg</t>
+          <t>Scotch Whisky Association</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AVR-ISLAY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Malt</t>
-        </is>
-      </c>
+          <t>Current operating Scotch whisky distillery list</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AVO-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AVP-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Imported from raw operating register; enrichment pending verification.</t>
+          <t>Canonical operating baseline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVD-CAOL-ILA</t>
+          <t>AVS-OFFICIAL-DISTILLERY-WEBSITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caol Ila</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Caol Ila</t>
+          <t>Distillery</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AVR-ISLAY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Malt</t>
-        </is>
-      </c>
+          <t>Official distillery website</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AVO-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AVP-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Imported from raw operating register; enrichment pending verification.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVD-CAMERONBRIDGE</t>
+          <t>AVS-OWNER-WEBSITE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cameronbridge</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cameronbridge</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AVR-LOWLANDS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
+          <t>Owner corporate website</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AVO-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AVP-UNKNOWN</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Imported from raw operating register; enrichment pending verification.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1205,9 +1297,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>distillery_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>official_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>preferred_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>region_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>founded_year</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>owner_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>parent_company_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AVD-ARDBEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ardbeg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ardbeg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AVR-ISLAY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Malt</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AVO-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AVD-CAOL-ILA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Caol Ila</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Caol Ila</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AVR-ISLAY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Malt</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AVO-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AVD-CAMERONBRIDGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cameronbridge</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cameronbridge</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AVR-LOWLANDS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AVO-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AVP-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Imported from raw operating register; enrichment pending verification.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1223,4 +1552,122 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evidence_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>field_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>field_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>evidence_strength</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verification_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verified_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AVE-000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>distillery</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AVD-ARDBEG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>official_name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ardbeg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AVS-OFFICIAL-DISTILLERY-WEBSITE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Local verification of evidence capture workflow</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/xlsx/UWRDB_release.xlsx
+++ b/exports/xlsx/UWRDB_release.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,6 +698,29 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AVP-SUNTORY-GLOBAL-SPIRITS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Suntory Global Spirits</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.suntoryglobalspirits.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -710,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,6 +847,34 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AVO-BEAM-SUNTORY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Beam Suntory</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AVP-SUNTORY-GLOBAL-SPIRITS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.suntoryglobalspirits.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -933,7 +984,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Production type: Malt, Grain, Malt &amp; Grain, Unknown</t>
+          <t>Production type</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -977,7 +1028,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>founded_year</t>
+          <t>owner_id</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -987,24 +1038,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Year the distillery was founded</t>
+          <t>Current operating owner</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Requires evidence</t>
+          <t>Gold requires curated owner</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>owner_id</t>
+          <t>parent_company_id</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1014,7 +1065,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Current operating owner</t>
+          <t>Ultimate controlling parent company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1024,14 +1075,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gold requires curated owner</t>
+          <t>Gold requires curated parent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>parent_company_id</t>
+          <t>founded_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1041,19 +1092,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ultimate controlling parent company</t>
+          <t>Year founded</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Gold requires curated parent</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1076,11 +1123,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Prefer HTTPS</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1103,11 +1146,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Gold geography target</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1130,11 +1169,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Gold geography target</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1433,27 +1468,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVD-CAOL-ILA</t>
+          <t>AVD-CAMERONBRIDGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caol Ila</t>
+          <t>Cameronbridge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Caol Ila</t>
+          <t>Cameronbridge</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AVR-ISLAY</t>
+          <t>AVR-LOWLANDS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malt</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1486,27 +1521,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVD-CAMERONBRIDGE</t>
+          <t>AVD-CAOL-ILA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cameronbridge</t>
+          <t>Caol Ila</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cameronbridge</t>
+          <t>Caol Ila</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AVR-LOWLANDS</t>
+          <t>AVR-ISLAY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Malt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1653,7 +1688,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1661,11 +1696,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Local verification of evidence capture workflow</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/xlsx/UWRDB_release.xlsx
+++ b/exports/xlsx/UWRDB_release.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="owner" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="distillery" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brand" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="region" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="parent_company" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="owner" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="field_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="source" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="distillery" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="brand" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="evidence" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
